--- a/Result/profitability/2536.xlsx
+++ b/Result/profitability/2536.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.41</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6599999999999999</v>
+        <v>0.91375</v>
       </c>
       <c r="N2" t="n">
-        <v>26.4275</v>
+        <v>23.66</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>3.7</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12</v>
+        <v>1.3125</v>
       </c>
       <c r="N3" t="n">
-        <v>25.9475</v>
+        <v>26.0025</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.97</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1775</v>
+        <v>1.43</v>
       </c>
       <c r="N4" t="n">
-        <v>26.43875</v>
+        <v>26.5375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.54</v>
       </c>
       <c r="M5" t="n">
-        <v>1.10625</v>
+        <v>1.21125</v>
       </c>
       <c r="N5" t="n">
-        <v>23.0825</v>
+        <v>22.65</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.64</v>
       </c>
       <c r="M6" t="n">
-        <v>1.16</v>
+        <v>1.4375</v>
       </c>
       <c r="N6" t="n">
-        <v>24.73125</v>
+        <v>23.945</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.58</v>
       </c>
       <c r="M7" t="n">
-        <v>1.37875</v>
+        <v>1.37</v>
       </c>
       <c r="N7" t="n">
-        <v>26.645</v>
+        <v>26.90125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>3.36</v>
       </c>
       <c r="M8" t="n">
-        <v>1.53375</v>
+        <v>1.77125</v>
       </c>
       <c r="N8" t="n">
-        <v>30.44375</v>
+        <v>30.27625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9802,6 +9802,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2536</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4105</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3238</v>
+      </c>
+      <c r="E75" t="n">
+        <v>867</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="G75" t="n">
+        <v>786</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>19.14%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-42</v>
+      </c>
+      <c r="J75" t="n">
+        <v>744</v>
+      </c>
+      <c r="K75" t="n">
+        <v>682</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24.86375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X75" t="n">
+        <v>12.66666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0596616206589492</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8399999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.6942148760330578</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.459999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1407648494711147</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
